--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6c51ee1e6bfdc4f0/1. Voltia/Cosas Nico/Reporte_Fotovoltaico/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{FA7FC9A3-D387-CA45-9740-697372029857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E362FDC5-653D-DD45-91C3-827DD2C5C48C}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{FA7FC9A3-D387-CA45-9740-697372029857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{523BAEA8-1F2A-9E47-B57C-8F2EC7C5A163}"/>
   <bookViews>
-    <workbookView xWindow="17120" yWindow="680" windowWidth="17080" windowHeight="20000" activeTab="1" xr2:uid="{ED5A8133-1C70-5642-9072-1075FB072BB4}"/>
+    <workbookView xWindow="17120" yWindow="680" windowWidth="17080" windowHeight="19860" activeTab="4" xr2:uid="{ED5A8133-1C70-5642-9072-1075FB072BB4}"/>
   </bookViews>
   <sheets>
     <sheet name="parametros" sheetId="1" r:id="rId1"/>
     <sheet name="precios_simple" sheetId="2" r:id="rId2"/>
     <sheet name="precios_doble" sheetId="3" r:id="rId3"/>
     <sheet name="precios_triple" sheetId="4" r:id="rId4"/>
+    <sheet name="zafral" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t>tarifa</t>
   </si>
@@ -87,6 +88,9 @@
   </si>
   <si>
     <t>hasta_kwh</t>
+  </si>
+  <si>
+    <t>zafral</t>
   </si>
 </sst>
 </file>
@@ -139,10 +143,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -462,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C386E9ED-A108-6D41-A270-797EE8E6AE81}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -547,6 +547,28 @@
         <v>70</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -680,4 +702,46 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8B98437-75D4-5749-8AE7-E02454655DB0}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>10.028</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>4.4109999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>2.0059999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>